--- a/output/pdf_financials_xlsx/AMT.xlsx
+++ b/output/pdf_financials_xlsx/AMT.xlsx
@@ -5455,46 +5455,46 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.03149</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.039301</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.111849</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.111849</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.111849</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.111849</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.562049</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.353751</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.445073</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.896184</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>16.570059</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>16.992919</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>17.589025</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>27.602653</v>
       </c>
     </row>
     <row r="93">
@@ -9849,7 +9849,11 @@
           <t>Reserves 15, 16</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11740,7 +11744,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13196,7 +13204,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15042,7 +15054,11 @@
           <t>Reserves 19</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -17889,7 +17905,11 @@
           <t>Reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -19903,7 +19923,11 @@
           <t>Reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -20872,7 +20896,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AMT.xlsx
+++ b/output/pdf_financials_xlsx/AMT.xlsx
@@ -885,34 +885,34 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.004929</v>
+        <v>0.06801400000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.010785</v>
+        <v>0.038689</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.000117</v>
+        <v>0.01602</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.032267</v>
+        <v>0.09958</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.043634</v>
+        <v>0.049666</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.031364</v>
+        <v>0.064693</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>1.056334</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.588032</v>
+        <v>2.759358</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.806546</v>
+        <v>6.304446</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.74452</v>
+        <v>7.337763</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>24.088497</v>
@@ -962,19 +962,19 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.031364</v>
+        <v>-0.064693</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.9435210000000001</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-2.416706</v>
+        <v>-2.588032</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.524549</v>
+        <v>-6.022449</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.658062</v>
+        <v>-7.251305</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-12.448349</v>
@@ -2235,31 +2235,31 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010083</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009023</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.266581</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.189175</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.141422</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.10719</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.269005</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.311487</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.24303</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>6.367533</v>
@@ -2343,31 +2343,31 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010083</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009023</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.266581</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.189175</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.141422</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.10719</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.269005</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.311487</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.24303</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>6.367533</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.011822</v>
+        <v>0.001739</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.014023</v>
+        <v>0.005</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.269081</v>
+        <v>0.0025</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3009,13 +3009,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.406042</v>
+        <v>0.137037</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.809327</v>
+        <v>0.49784</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.634617</v>
+        <v>0.391587</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>1.141756</v>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -51567,7 +51567,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E486" s="5" t="n">
@@ -51592,7 +51592,7 @@
         <v>0.051254</v>
       </c>
       <c r="L486" s="5" t="n">
-        <v>-2.759358</v>
+        <v>2.759358</v>
       </c>
       <c r="M486" s="5" t="n">
         <v>6.304446</v>
@@ -54932,7 +54932,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -54966,10 +54966,10 @@
         </is>
       </c>
       <c r="K523" s="5" t="n">
-        <v>-1.169147</v>
+        <v>1.169147</v>
       </c>
       <c r="L523" s="5" t="n">
-        <v>-2.759358</v>
+        <v>2.759358</v>
       </c>
       <c r="M523" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AMT.xlsx
+++ b/output/pdf_financials_xlsx/AMT.xlsx
@@ -1966,22 +1966,22 @@
         <v>0.376859</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.508247</v>
+        <v>0.555754</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.740656</v>
+        <v>1.411616</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.279613</v>
+        <v>0.977621</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.669633</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.038172</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.46743</v>
       </c>
     </row>
     <row r="29">
@@ -2018,22 +2018,22 @@
         <v>-6.198461</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.833281</v>
+        <v>-7.785774</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-15.449972</v>
+        <v>-14.779012</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-30.259334</v>
+        <v>-29.561326</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-21.773865</v>
+        <v>-21.104232</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6.229527</v>
+        <v>6.267699</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-12.250171</v>
+        <v>-11.782741</v>
       </c>
     </row>
     <row r="30">
@@ -2082,22 +2082,22 @@
         <v>-2198.059199211339</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-391.9076205861943</v>
+        <v>-389.5307933880907</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-64.54434450984394</v>
+        <v>-61.74131849838418</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-246.9109463351808</v>
+        <v>-241.2153214470214</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-759.3721522059909</v>
+        <v>-736.0184365290472</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>288.2873781627249</v>
+        <v>290.0538856036956</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-748.0010942034693</v>
+        <v>-719.4596027040014</v>
       </c>
     </row>
     <row r="31">
@@ -5854,28 +5854,28 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.278503</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.376859</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.508247</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.411616</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.977621</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.669633</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.038172</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.46743</v>
       </c>
     </row>
     <row r="101">
@@ -21968,7 +21968,11 @@
           <t>Depreciation of right of use assets (note 10)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -25091,7 +25095,11 @@
           <t>Depreciation of right of use assets (note 13)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -27065,7 +27073,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -28252,7 +28260,11 @@
           <t>Addition to intangible asset</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -29245,7 +29257,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -29425,7 +29437,11 @@
           <t>Depreciation of right of use assets (note 15)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -30424,7 +30440,11 @@
           <t>Addition to intangible asset (note 14)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -31783,7 +31803,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -40565,7 +40585,11 @@
           <t>Depreciation of right of use assets (note 10)</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -43348,7 +43372,11 @@
           <t>Depreciation of right of use assets (note 12)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -46058,7 +46086,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -46151,7 +46179,11 @@
           <t>Depreciation of right of use assets (note 13)</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -48754,7 +48786,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -48934,7 +48966,11 @@
           <t>Depreciation of right of use assets (note 15)</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -50568,7 +50604,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -50659,7 +50695,11 @@
           <t>Amortization of tangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -53290,7 +53330,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
